--- a/tests/fixtures/modeles/Modele_Correspondance_SIEOL.xlsx
+++ b/tests/fixtures/modeles/Modele_Correspondance_SIEOL.xlsx
@@ -42,7 +42,7 @@
     <t>Numéro court travail SIEOL</t>
   </si>
   <si>
-    <t>16299151001</t>
+    <t>00000051001</t>
   </si>
   <si>
     <t>51001</t>
@@ -54,7 +54,7 @@
     <t>59001</t>
   </si>
   <si>
-    <t>16194751001</t>
+    <t>00000351001</t>
   </si>
   <si>
     <t>250001</t>
@@ -63,7 +63,7 @@
     <t>501</t>
   </si>
   <si>
-    <t>16352711560</t>
+    <t>00000211560</t>
   </si>
   <si>
     <t>11560</t>
@@ -105,7 +105,7 @@
     <t>Détail des colonnes</t>
   </si>
   <si>
-    <t>Numéro EID complet (11 chiffres) — obligatoire. C'est la clé qui permet à Ovilog de retrouver la fiche de l'animal. Format : le numéro EID national tel que scanné, sans le préfixe pays (ex: 16299151001).</t>
+    <t>Numéro EID complet (11 chiffres) — obligatoire. C'est la clé qui permet à Ovilog de retrouver la fiche de l'animal. Format : le numéro EID national tel que scanné, sans le préfixe pays (ex: 00000051001).</t>
   </si>
   <si>
     <t>Numéro officiel Ovilog — informatif seulement (les 5 derniers chiffres de l'EID), pas nécessaire de le remplir si l'EID est déjà renseigné.</t>
